--- a/output/pdf_financials_xlsx/WPG.xlsx
+++ b/output/pdf_financials_xlsx/WPG.xlsx
@@ -922,31 +922,31 @@
         <v>0.551669</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.030591</v>
+        <v>0.700659</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.028899</v>
+        <v>11.970455</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.017302</v>
+        <v>0.536455</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.016116</v>
+        <v>0.60049</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.012606</v>
+        <v>0.353614</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.012047</v>
+        <v>0.260676</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.012635</v>
+        <v>0.447993</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.028854</v>
+        <v>0.406014</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.016681</v>
+        <v>0.256871</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>0.9234599999999999</v>
@@ -955,13 +955,13 @@
         <v>0.656524</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.032082</v>
+        <v>0.420385</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.209991</v>
+        <v>1.061213</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>3.594618</v>
+        <v>10.584215</v>
       </c>
     </row>
     <row r="11">
@@ -980,31 +980,31 @@
         <v>-0.551669</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.030591</v>
+        <v>-0.700659</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.028899</v>
+        <v>-11.970455</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.017302</v>
+        <v>-0.536455</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.016116</v>
+        <v>-0.60049</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.012606</v>
+        <v>-0.353614</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.012047</v>
+        <v>-0.260676</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.012635</v>
+        <v>-0.447993</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.028854</v>
+        <v>-0.406014</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.016681</v>
+        <v>-0.256871</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>-0.9234599999999999</v>
@@ -1013,13 +1013,13 @@
         <v>-0.656524</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.032082</v>
+        <v>-0.420385</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.209991</v>
+        <v>-1.061213</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-3.594618</v>
+        <v>-10.584215</v>
       </c>
     </row>
     <row r="12">
@@ -1029,28 +1029,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.02594</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000171</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001518</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.006876</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.00194</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002276</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>5.5e-05</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.009302</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.094608</v>
       </c>
     </row>
     <row r="13">
@@ -1993,28 +1993,28 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.4881</v>
+        <v>-0.5140400000000001</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.305451</v>
+        <v>-0.305622</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.38856</v>
+        <v>-2.390078</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.451841</v>
+        <v>1.444965</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-11.959874</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.877485</v>
+        <v>0.875545</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.598214</v>
+        <v>-0.60049</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.340548</v>
+        <v>-0.340603</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.088118</v>
@@ -2038,10 +2038,10 @@
         <v>-0.420385</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.051911</v>
+        <v>-1.042609</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-10.489607</v>
+        <v>-10.394999</v>
       </c>
     </row>
     <row r="28">
@@ -2109,28 +2109,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.4881</v>
+        <v>-0.5140400000000001</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.305451</v>
+        <v>-0.305622</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.38856</v>
+        <v>-2.390078</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.451841</v>
+        <v>1.444965</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-11.959874</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.877485</v>
+        <v>0.875545</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.598214</v>
+        <v>-0.60049</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.340548</v>
+        <v>-0.340603</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.088118</v>
@@ -2154,10 +2154,10 @@
         <v>-0.420385</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.051911</v>
+        <v>-1.042609</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-10.489607</v>
+        <v>-10.394999</v>
       </c>
     </row>
     <row r="30">
@@ -2422,40 +2422,40 @@
         <v>0.18587</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.18587</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.381319</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.070365</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.21424</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.091478</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.05007</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.013589</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.089541</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.021468</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.047168</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.012376</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.431959</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.090187</v>
@@ -2538,40 +2538,40 @@
         <v>0.18587</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.199928</v>
+        <v>1.385798</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.199928</v>
+        <v>1.581247</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.070365</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.514168</v>
+        <v>0.7284080000000001</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.085993</v>
+        <v>0.177471</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.05007</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.013589</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.089541</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.021468</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.047168</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.012376</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.431959</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.090187</v>
@@ -3240,34 +3240,34 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.081384</v>
+        <v>0.011019</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.221776</v>
+        <v>0.007536</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.099192</v>
+        <v>0.007714</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.055725</v>
+        <v>0.005655</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.01797</v>
+        <v>0.004381</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.09810099999999999</v>
+        <v>0.00856</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.049834</v>
+        <v>0.028366</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.052617</v>
+        <v>0.005449</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.276154</v>
+        <v>0.263778</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.504294</v>
+        <v>0.072335</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.034938</v>
@@ -9013,7 +9013,11 @@
           <t>Reclamation deposits (note 6)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -10557,7 +10561,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10735,7 +10739,11 @@
           <t>Reclamation deposit (note 5)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -13679,7 +13687,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -16902,7 +16910,11 @@
           <t>Reclamation deposits (note 6)</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -26709,7 +26721,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -26723,10 +26735,10 @@
         </is>
       </c>
       <c r="G188" s="5" t="n">
-        <v>-0.551669</v>
+        <v>0.551669</v>
       </c>
       <c r="H188" s="5" t="n">
-        <v>-0.700659</v>
+        <v>0.700659</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -26759,10 +26771,10 @@
         </is>
       </c>
       <c r="O188" s="5" t="n">
-        <v>-0.406014</v>
+        <v>0.406014</v>
       </c>
       <c r="P188" s="5" t="n">
-        <v>-0.256871</v>
+        <v>0.256871</v>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
@@ -26800,7 +26812,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -28379,7 +28391,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -28398,28 +28410,28 @@
         </is>
       </c>
       <c r="H206" s="5" t="n">
-        <v>-0.700659</v>
+        <v>0.700659</v>
       </c>
       <c r="I206" s="5" t="n">
-        <v>-11.970455</v>
+        <v>11.970455</v>
       </c>
       <c r="J206" s="5" t="n">
-        <v>-0.536455</v>
+        <v>0.536455</v>
       </c>
       <c r="K206" s="5" t="n">
-        <v>-0.60049</v>
+        <v>0.60049</v>
       </c>
       <c r="L206" s="5" t="n">
-        <v>-0.353614</v>
+        <v>0.353614</v>
       </c>
       <c r="M206" s="5" t="n">
-        <v>-0.260676</v>
+        <v>0.260676</v>
       </c>
       <c r="N206" s="5" t="n">
-        <v>-0.447993</v>
+        <v>0.447993</v>
       </c>
       <c r="O206" s="5" t="n">
-        <v>-0.406014</v>
+        <v>0.406014</v>
       </c>
       <c r="P206" t="inlineStr">
         <is>
@@ -29066,7 +29078,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -32884,7 +32896,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E251" s="5" t="n">

--- a/output/pdf_financials_xlsx/WPG.xlsx
+++ b/output/pdf_financials_xlsx/WPG.xlsx
@@ -4247,43 +4247,43 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.025881</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.046701</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.013441</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.084192</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.075888</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.13649</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.054617</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.19752</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.282478</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.204221</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.053461</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.15198</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.30619</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>0</v>
@@ -4421,43 +4421,43 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.073312</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.179067</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.06275</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.059696</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.040721</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.051164</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.118071</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.106942</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.042763</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.043846</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.038822</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>0</v>
@@ -7296,7 +7296,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>2.222548</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -7320,7 +7320,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.032757</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
@@ -20837,7 +20837,11 @@
           <t>Proceeds from sale of marketable securities (note 6)</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -24708,7 +24712,11 @@
           <t>Proceeds from short-term investments</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -25211,7 +25219,11 @@
           <t>Recovery of future income taxes</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
